--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2965,6 +2965,129 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113600106</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56743</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100020</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Berguv</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bubo bubo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Orust, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>302031</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6454469</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orust</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Röra</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>1906-11-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1906-11-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En ad. hona, inköpt Inköpt av Gustaf Kihlén, från Orust 14 Nov 1906, förvaras på GNM: Av su: 2984 (ID:8098).</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>113600106</v>
       </c>
       <c r="B21" t="n">
-        <v>56743</v>
+        <v>56744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>113600106</v>
       </c>
       <c r="B21" t="n">
-        <v>56744</v>
+        <v>56746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -2970,7 +2970,7 @@
         <v>113600106</v>
       </c>
       <c r="B21" t="n">
-        <v>56746</v>
+        <v>56774</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2965,129 +2965,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>113600106</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57227</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100020</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Berguv</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Bubo bubo</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Orust, Boh</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>302031</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6454469</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Orust</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Röra</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>1906-11-14</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>1906-11-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En ad. hona, inköpt Inköpt av Gustaf Kihlén, från Orust 14 Nov 1906, förvaras på GNM: Av su: 2984 (ID:8098).</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Rune Hixén</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Via Rune Hixén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -2369,7 +2369,7 @@
         <v>88267075</v>
       </c>
       <c r="B16" t="n">
-        <v>56869</v>
+        <v>56870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 775-2023 artfynd.xlsx
+++ b/artfynd/A 775-2023 artfynd.xlsx
@@ -2369,7 +2369,7 @@
         <v>88267075</v>
       </c>
       <c r="B16" t="n">
-        <v>56870</v>
+        <v>56874</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
